--- a/Supplementary Files/Supplementary_File_SF3.xlsx
+++ b/Supplementary Files/Supplementary_File_SF3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Reference</t>
   </si>
@@ -22,24 +22,9 @@
     <t>Target</t>
   </si>
   <si>
-    <t>Bit-packing</t>
-  </si>
-  <si>
     <t>Compressors</t>
   </si>
   <si>
-    <t>Bit-packing + HiRGC</t>
-  </si>
-  <si>
-    <t>Bit-packing + SCCG</t>
-  </si>
-  <si>
-    <t>Bit-packing + HRCM</t>
-  </si>
-  <si>
-    <t>Bit-packing + RGCOK</t>
-  </si>
-  <si>
     <t>HGC</t>
   </si>
   <si>
@@ -107,6 +92,18 @@
   </si>
   <si>
     <t>Table 4: Compressed file sizes (KiB) of other species' data sets by HGC and four state-of-the-art methods.</t>
+  </si>
+  <si>
+    <t>NF + HiRGC</t>
+  </si>
+  <si>
+    <t>NF + SCCG</t>
+  </si>
+  <si>
+    <t>NF + HRCM</t>
+  </si>
+  <si>
+    <t>NF + RGCOK</t>
   </si>
 </sst>
 </file>
@@ -675,7 +672,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -768,29 +765,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -1140,25 +1134,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="11" customWidth="1"/>
     <col min="2" max="2" width="18.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.28515625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="11" customWidth="1"/>
-    <col min="8" max="10" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="11"/>
+    <col min="4" max="5" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="11" customWidth="1"/>
+    <col min="7" max="9" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="25"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -1174,23 +1167,21 @@
       <c r="M1" s="25"/>
       <c r="N1" s="25"/>
       <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="Q2" s="25"/>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" thickBot="1">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="P2" s="25"/>
+    </row>
+    <row r="3" spans="1:16" ht="16.5" thickBot="1">
       <c r="A3" s="20"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -1199,531 +1190,491 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="I3" s="26"/>
       <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
+      <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
       <c r="N3" s="24"/>
       <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="25"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="35" t="s">
+      <c r="P3" s="25"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1">
+      <c r="A4" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="36" t="s">
+      <c r="C4" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="19"/>
       <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
+      <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-    </row>
-    <row r="5" spans="1:17" ht="48" thickBot="1">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="27"/>
+    </row>
+    <row r="5" spans="1:16" ht="32.25" thickBot="1">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="23"/>
       <c r="L5" s="23"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
       <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-    </row>
-    <row r="6" spans="1:17">
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="13" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="8">
         <v>118342</v>
       </c>
-      <c r="D6" s="8">
-        <v>29585.5</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="D6" s="13">
         <v>29587.03</v>
       </c>
-      <c r="F6" s="12">
+      <c r="E6" s="12">
         <v>29587.15</v>
       </c>
+      <c r="F6" s="13">
+        <v>29588.45</v>
+      </c>
       <c r="G6" s="13">
-        <v>29588.45</v>
-      </c>
-      <c r="H6" s="13">
         <v>29588.01</v>
       </c>
-      <c r="I6" s="21">
+      <c r="H6" s="21">
         <v>27878.31</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="27"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="23"/>
       <c r="L6" s="23"/>
       <c r="M6" s="23"/>
       <c r="N6" s="23"/>
       <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-    </row>
-    <row r="7" spans="1:17">
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" s="8">
         <v>118342</v>
       </c>
-      <c r="D7" s="8">
-        <v>29585.5</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="D7" s="13">
         <v>29586.95</v>
       </c>
-      <c r="F7" s="12">
+      <c r="E7" s="12">
         <v>29587.1</v>
       </c>
+      <c r="F7" s="13">
+        <v>29588.400000000001</v>
+      </c>
       <c r="G7" s="13">
-        <v>29588.400000000001</v>
-      </c>
-      <c r="H7" s="13">
         <v>29588.01</v>
       </c>
-      <c r="I7" s="16">
+      <c r="H7" s="16">
         <v>27878.37</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="27"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="23"/>
       <c r="L7" s="23"/>
       <c r="M7" s="23"/>
       <c r="N7" s="23"/>
       <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-    </row>
-    <row r="8" spans="1:17">
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="13" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" s="8">
         <v>199789</v>
       </c>
-      <c r="D8" s="8">
-        <v>49947.25</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="D8" s="13">
         <v>50385.52</v>
       </c>
-      <c r="F8" s="12">
+      <c r="E8" s="12">
         <v>50392.57</v>
       </c>
+      <c r="F8" s="13">
+        <v>50167.19</v>
+      </c>
       <c r="G8" s="13">
-        <v>50167.19</v>
-      </c>
-      <c r="H8" s="13">
         <v>50157.39</v>
       </c>
-      <c r="I8" s="21">
+      <c r="H8" s="21">
         <v>22929.83</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="27"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="23"/>
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
       <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-    </row>
-    <row r="9" spans="1:17">
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C9" s="8">
         <v>199784</v>
       </c>
-      <c r="D9" s="8">
-        <v>49946</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="D9" s="13">
         <v>50380.45</v>
       </c>
-      <c r="F9" s="12">
+      <c r="E9" s="12">
         <v>50388.65</v>
       </c>
+      <c r="F9" s="13">
+        <v>50163.58</v>
+      </c>
       <c r="G9" s="13">
-        <v>50163.58</v>
-      </c>
-      <c r="H9" s="13">
         <v>50153.22</v>
       </c>
-      <c r="I9" s="21">
+      <c r="H9" s="21">
         <v>22928.65</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="27"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="23"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
       <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-    </row>
-    <row r="10" spans="1:17">
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10" s="8">
         <v>199784</v>
       </c>
-      <c r="D10" s="8">
-        <v>49946</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="D10" s="13">
         <v>50429.46</v>
       </c>
-      <c r="F10" s="12">
+      <c r="E10" s="12">
         <v>50437.86</v>
       </c>
+      <c r="F10" s="13">
+        <v>50921.03</v>
+      </c>
       <c r="G10" s="13">
-        <v>50921.03</v>
-      </c>
-      <c r="H10" s="13">
         <v>50221.1</v>
       </c>
-      <c r="I10" s="21">
+      <c r="H10" s="21">
         <v>22929.98</v>
       </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="27"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
       <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-    </row>
-    <row r="11" spans="1:17">
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C11" s="8">
         <v>740224</v>
       </c>
-      <c r="D11" s="8">
-        <v>185056</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="D11" s="13">
         <v>185423.11</v>
       </c>
-      <c r="F11" s="12">
+      <c r="E11" s="12">
         <v>185428.4</v>
       </c>
+      <c r="F11" s="13">
+        <v>185427.24</v>
+      </c>
       <c r="G11" s="13">
-        <v>185427.24</v>
-      </c>
-      <c r="H11" s="13">
         <v>185417.82</v>
       </c>
-      <c r="I11" s="21">
+      <c r="H11" s="21">
         <v>85239.93</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="27"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="23"/>
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
       <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-    </row>
-    <row r="12" spans="1:17">
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="8">
         <v>739986</v>
       </c>
-      <c r="D12" s="8">
-        <v>184996.5</v>
-      </c>
-      <c r="E12" s="13">
+      <c r="D12" s="13">
         <v>185345.95</v>
       </c>
-      <c r="F12" s="12">
+      <c r="E12" s="12">
         <v>185250.94</v>
       </c>
+      <c r="F12" s="13">
+        <v>185272.26</v>
+      </c>
       <c r="G12" s="13">
-        <v>185272.26</v>
-      </c>
-      <c r="H12" s="13">
         <v>185283.64</v>
       </c>
-      <c r="I12" s="16">
+      <c r="H12" s="16">
         <v>85231.84</v>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="27"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="23"/>
       <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-    </row>
-    <row r="13" spans="1:17">
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" s="8">
         <v>739064</v>
       </c>
-      <c r="D13" s="8">
-        <v>184766</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="D13" s="13">
         <v>184985.65</v>
       </c>
-      <c r="F13" s="12">
+      <c r="E13" s="12">
         <v>184991.89</v>
       </c>
+      <c r="F13" s="13">
+        <v>184965.94</v>
+      </c>
       <c r="G13" s="13">
-        <v>184965.94</v>
-      </c>
-      <c r="H13" s="13">
         <v>184938.79</v>
       </c>
-      <c r="I13" s="21">
+      <c r="H13" s="21">
         <v>85279.33</v>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="27"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="23"/>
       <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-    </row>
-    <row r="14" spans="1:17">
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C14" s="8">
         <v>12109</v>
       </c>
-      <c r="D14" s="8">
-        <v>3027.25</v>
+      <c r="D14" s="13">
+        <v>3030.24</v>
       </c>
       <c r="E14" s="13">
-        <v>3030.24</v>
+        <v>3033.29</v>
       </c>
       <c r="F14" s="13">
-        <v>3033.29</v>
+        <v>3033.45</v>
       </c>
       <c r="G14" s="13">
-        <v>3033.45</v>
-      </c>
-      <c r="H14" s="13">
         <v>3034.23</v>
       </c>
-      <c r="I14" s="21">
+      <c r="H14" s="21">
         <v>2930.16</v>
       </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="27"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="23"/>
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
       <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-    </row>
-    <row r="15" spans="1:17" ht="16.5" thickBot="1">
+    </row>
+    <row r="15" spans="1:16" ht="16.5" thickBot="1">
       <c r="A15" s="30" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C15" s="18">
         <v>12109</v>
       </c>
-      <c r="D15" s="18">
-        <v>3027.25</v>
+      <c r="D15" s="30">
+        <v>3030.12</v>
       </c>
       <c r="E15" s="30">
-        <v>3030.12</v>
+        <v>3033.14</v>
       </c>
       <c r="F15" s="30">
-        <v>3033.14</v>
+        <v>3033.47</v>
       </c>
       <c r="G15" s="30">
-        <v>3033.47</v>
-      </c>
-      <c r="H15" s="30">
         <v>3034.01</v>
       </c>
-      <c r="I15" s="31">
+      <c r="H15" s="31">
         <v>2928.96</v>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="27"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="23"/>
       <c r="L15" s="23"/>
       <c r="M15" s="23"/>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-    </row>
-    <row r="16" spans="1:17">
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="20"/>
       <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="27"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="23"/>
       <c r="L16" s="23"/>
       <c r="M16" s="23"/>
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-    </row>
-    <row r="17" spans="1:17">
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="29" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
+      <c r="D17" s="27"/>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
+      <c r="G17" s="20"/>
       <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="27"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="23"/>
       <c r="L17" s="23"/>
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-    </row>
-    <row r="18" spans="1:17">
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="33" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="27"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
       <c r="N18" s="23"/>
       <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-    </row>
-    <row r="19" spans="1:17">
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="9"/>
       <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
       <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-    </row>
-    <row r="20" spans="1:17">
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="9"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="23"/>
       <c r="L20" s="23"/>
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-    </row>
-    <row r="21" spans="1:17">
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="16"/>
       <c r="B21" s="32"/>
       <c r="C21" s="14"/>
@@ -1733,47 +1684,44 @@
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="2"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="4"/>
       <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="16"/>
       <c r="B22" s="2"/>
       <c r="C22" s="4"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="2"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="4"/>
       <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="16"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="14"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="17"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-    </row>
-    <row r="24" spans="1:17">
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
@@ -1784,9 +1732,8 @@
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-    </row>
-    <row r="25" spans="1:17">
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -1803,66 +1750,60 @@
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-    </row>
-    <row r="26" spans="1:17">
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="1:17">
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-    </row>
-    <row r="28" spans="1:17">
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:16">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-    </row>
-    <row r="30" spans="1:17">
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="14"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="14"/>
+      <c r="O30" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
